--- a/output/第10期計画_発注者確認事項一覧.xlsx
+++ b/output/第10期計画_発注者確認事項一覧.xlsx
@@ -10,7 +10,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_この一覧について" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_委員会決定事項一覧" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_決定の優先順位と期限" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_残る課題と当方の見解" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -562,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -579,7 +578,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（協議用素案・令和8年8月時点）に残る［要協議］63件・［要確認］15件・「未対応」7件・［要内訳］4件・「暫定」1件の計90箇所を、ご決定いただく単位で12件に集約したものです。委員会には本一覧を用い、本文を直接お読みいただくことは想定していません。</t>
+          <t>計画素案（協議用素案・令和8年8月時点）に残る［要協議］63件・［要確認］15件・「未対応」7件・［要内訳］4件・「暫定」1件の計90箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
         </is>
       </c>
     </row>
@@ -626,39 +625,27 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>03_残る課題と当方の見解</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>そのままでは採れないご提案、及び補足を要する事項についての受託者の見解です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>【ご留意いただきたいこと】</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="150" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="10" ht="150" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>1　本一覧の「受託者の推奨案」は、現時点で受領している資料の範囲による受託者の案です。ご決定は発注者及び策定委員会において行っていただくものです。
 2　計画素案の本文には、［要協議］［要確認］［要内訳］のプレースホルダをそのまま残しています。本文に確認事項の注記を書かず、本一覧及び「計画素案の別管理表」で一元管理する運用によるものです。
 3　資料提供依頼No.13（令和6〜8年度の施策・事業実績）の受領により自動的に解消する箇所が含まれます。
-4　受託者の作業過程における点検の記録は、「レビュー対応記録」として別に保管しています。ご確認をご希望の場合はお申し付けください。</t>
+4　受託者の作業過程における点検の記録は、業務仕様書４（10）「その他業務で作成した資料　一式」として別に保管しています。ご確認をご希望の場合はお申し付けください。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A10:B10"/>
   </mergeCells>
@@ -697,7 +684,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>協議用素案（令和8年8月時点）に残る［要協議］63件・［要確認］15件・「未対応」7件・［要内訳］4件・「暫定」1件の計90箇所を、決定の単位で12件にまとめた。委員会には本一覧を用い、本文を直接読ませない。</t>
+          <t>協議用素案（令和8年8月時点）に残る［要協議］63件・［要確認］15件・「未対応」7件・［要内訳］4件・「暫定」1件の計90箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
         </is>
       </c>
     </row>
@@ -1011,7 +998,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>施策の空白5領域の扱い</t>
+          <t>調査に所見があるが対応する施策を確認できない5領域の扱い</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1024,7 +1011,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>移動・交通、経済的理由による未利用、人生の最終段階における意思決定支援、身寄りのない高齢者、未利用認定者への働きかけを、①広域連合の計画で扱う／②3町の計画に委ねる</t>
+          <t>移動・交通、未利用の理由の把握、人生の最終段階における意思決定支援、身寄りのない高齢者、未利用認定者への働きかけを、①広域連合の計画で扱う／②3町の計画に委ねる</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1353,10 +1340,10 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="39" customHeight="1">
+    <row r="17" ht="52" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>注1）箇所数の合計は87箇所である。本文の90箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る3箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。</t>
+          <t>注1）箇所数の合計は87箇所である。本文の90箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る3箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2342,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>決定6　施策の空白5領域の扱い</t>
+          <t>決定6　調査に所見があるが対応する施策を確認できない5領域の扱い</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -2734,235 +2721,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>残る課題と、当方の見解</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="52" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>点検で挙がった提案のうち、そのままでは採れないもの及び補足を要するものについて当方の見解を述べる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="4" t="inlineStr"/>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>レビューの提案</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>当方の見解</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>理由</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>対応</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="76" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>委員会に出す表から「対応中」をなくす（P1-4）</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>そのままでは満たせない</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>第9期評価の指摘29件のうち、資料の受領を待つものが含まれる。これらを「対応中」から外すには資料が要る。資料待ちであることを隠すと、かえって評価の確からしさを誤って伝えることになる。</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>「資料待ち」と「対応中」を分けて表示する。資料待ちの件数と内容を明示する</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="76" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>本文の要協議番号と別管理表のIDを完全一致させる（P2-4）</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>本文へのID付与は採らない</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>計画本文は住民及び委員が読むものであり、内部管理用のIDを本文に置くと読みにくくなる。章節で特定できるため、決定事項一覧の側で対応させる方が実務に合う。</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>03シートで章節別に対応させた。本文へのID付与の要否は発注者の決定による</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="76" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>調査分析95％は「分析成果物の作成率」であり「確定値の受入率」ではない（5章）</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>そのとおりである</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>当方の工程管理表は作成率で進捗を示していた。確定値の受入率で見ると、確定値表10件のうち確定は2件（20％）である。</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>業務工程管理表に「作成率」と「確定値の受入率」の2つの欄を設ける</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="76" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>8月末を「未受領時の扱いも含めて評価方法を確定する締切」とする（7章）</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>同意する</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>資料の受領を待って全体が止まることを避けられる。当方も暫定評価ルールを用意した。</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>決定5として発注者の承認を求める</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="76" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>⑤</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>資料提供依頼の番号が2つの管理表で異なる</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>当方の管理上の不備である</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>業務工程管理表06シートでは「No.13」、必要事項の一覧では「No.1」として同じ資料（令和6〜8年度の施策・事業実績）を管理していた。レビューはNo.13で参照しており、外部から見ると同定できない。</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>番号を業務工程管理表06シートに統一する。本改訂では未着手であり、次回の改訂で行う</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="76" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>⑥</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>全体進捗60％への更新（5章）</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>妥当である</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>第9期評価65％（実績未受領のため75％から引下げ）、成果品45％（索引・版の是正を要する）等の引下げはいずれも根拠がある。</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>業務工程管理表に反映する。本改訂では未着手であり、次回の改訂で行う</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>注1）⑤（資料提供依頼の番号の不統一）は、レビューの指摘には含まれていないが、レビューがNo.13と参照していることから当方が気づいたものである。同じ資料を2つの番号で管理しており、発注者に混乱を生じさせている。注2）⑤⑥は本改訂では未着手である。業務工程管理表と必要事項の一覧の改訂は次回にまとめて行う。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A12:E12"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/output/第10期計画_発注者確認事項一覧.xlsx
+++ b/output/第10期計画_発注者確認事項一覧.xlsx
@@ -866,7 +866,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>区域内に事業所が存在しない4サービスについて、整備するか区域外利用を前提とするかを決定いただきたい。H12（20.4％）はこの決定の根拠となる。</t>
+          <t>区域内に事業所が存在しない4サービスについて、整備するか区域外利用を前提とするかを決定いただきたい。H12の代理指標20.4％は、この検討の参考情報の一つとする（在宅生活の維持が難しい利用者98票中20票の割合であり、在宅利用者全体の未充足率ではない）。整備の可否は、給付実績、町外利用、待機、事業者の参入意向・人員確保、利用意向及び費用影響を併せて判断する。</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">

--- a/output/第10期計画_発注者確認事項一覧.xlsx
+++ b/output/第10期計画_発注者確認事項一覧.xlsx
@@ -59,7 +59,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -73,12 +73,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DEEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -157,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -185,7 +195,13 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -578,7 +594,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（協議用素案・令和8年8月時点）に残る［要協議］63件・［要確認］15件・「未対応」7件・［要内訳］4件・「暫定」1件の計90箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
+          <t>計画素案に残る要協議58件／要確認16件／未対応7件／要内訳1件／暫定6件 の計88箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
         </is>
       </c>
     </row>
@@ -659,32 +675,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>委員会決定事項一覧（本文の未決事項90箇所を12件に集約）</t>
+          <t>委員会決定事項一覧（本文の未決事項を12件に集約）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>協議用素案（令和8年8月時点）に残る［要協議］63件・［要確認］15件・「未対応」7件・［要内訳］4件・「暫定」1件の計90箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
+          <t>計画素案に残る要協議58件／要確認16件／未対応7件／要内訳1件／暫定6件 の計88箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
         </is>
       </c>
     </row>
@@ -731,10 +749,21 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>期限</t>
+          <t>ご回答
+(R8.9.3)</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>ご回答の内容</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>決定が必要になる時期</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>優先</t>
         </is>
@@ -779,12 +808,22 @@
           <t>発注者・3町</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>優先度は高いが、広域内部又は構成町との協議を行った上で決定</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>3町協議（R8.10・11）</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
@@ -829,12 +868,22 @@
           <t>発注者・策定委員会</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>3町協議（R8.10・11）</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
@@ -879,12 +928,22 @@
           <t>発注者・策定委員会・北海道</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>R8.11</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>3町の回答後（R8.11）</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -929,12 +988,22 @@
           <t>発注者・策定委員会</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>同上。代表KPIの再整理案（確認事項No.75）の了承後に協議</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>KPI再整理案の了承後</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -979,12 +1048,22 @@
           <t>発注者</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>現時点で回答可能。受託者案②を基本とする【了承済】</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>了承済（R8.9.3）</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1029,12 +1108,22 @@
           <t>発注者・3町・策定委員会</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>広域連合内部又は構成町との協議を行った上で決定</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>3町協議（R8.10・11）</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1079,12 +1168,22 @@
           <t>発注者</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>同上。受託者の推奨案及びその理由を改めて提示（内部確認結果への対応整理 03シートで提示済み）</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>R8.9（推奨案の提示後）</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
@@ -1129,12 +1228,22 @@
           <t>発注者・策定委員会</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>R8.11</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>3町の回答後（R8.11）</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1179,12 +1288,22 @@
           <t>発注者・策定委員会・北海道</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="inlineStr">
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>→</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>今後の分析・推計及び計画案の作成状況を踏まえて決定</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>計画案の作成状況による</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1229,12 +1348,22 @@
           <t>発注者</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>R8.11</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>→</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>計画案の作成状況による</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1279,12 +1408,22 @@
           <t>発注者・策定委員会</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>→</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>計画案の作成状況による</t>
+        </is>
+      </c>
+      <c r="L15" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1329,12 +1468,22 @@
           <t>発注者</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>計画全体の構成が見えてから決定。パブリックコメントの取扱いも併せて整理</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>計画全体の構成の確定後</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1343,14 +1492,14 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>注1）箇所数の合計は87箇所である。本文の90箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る3箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
+          <t>注1）箇所数の合計は87箇所である。本文の88箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る1箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>【章節別の未決箇所（90箇所の所在）】</t>
+          <t>【章節別の未決箇所（88箇所の所在）】</t>
         </is>
       </c>
     </row>
@@ -1405,19 +1554,19 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>第6節　計画の進行管理・推進体制</t>
+          <t>第1節 高齢者の状況</t>
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>0</v>
@@ -1433,7 +1582,7 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>決定5</t>
+          <t>決定1</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr"/>
@@ -1446,17 +1595,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0</v>
@@ -1465,11 +1614,11 @@
         <v>0</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>決定1</t>
+          <t>決定11</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr"/>
@@ -1482,17 +1631,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第5節 在宅介護の実態</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0</v>
@@ -1505,7 +1654,7 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>決定11</t>
+          <t>決定7</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr"/>
@@ -1518,17 +1667,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>0</v>
@@ -1554,17 +1703,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第8節 中長期推計からみた需要と財政</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F25" s="7" t="n">
         <v>0</v>
@@ -1577,7 +1726,7 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>決定7</t>
+          <t>決定2</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr"/>
@@ -1585,25 +1734,25 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>第8節 中長期推計からみた需要と財政</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="E26" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>0</v>
@@ -1613,7 +1762,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>決定2</t>
+          <t>決定10</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr"/>
@@ -1621,25 +1770,25 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>第5節 第9期計画の評価と第10期への課題</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>0</v>
@@ -1649,7 +1798,7 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>決定5</t>
+          <t>決定4</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr"/>
@@ -1657,22 +1806,22 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="7" t="n">
         <v>0</v>
@@ -1685,7 +1834,7 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>決定4</t>
+          <t>決定6</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr"/>
@@ -1698,17 +1847,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" s="7" t="n">
         <v>0</v>
@@ -1734,14 +1883,14 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>0</v>
@@ -1770,17 +1919,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" s="7" t="n">
         <v>4</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="7" t="n">
         <v>0</v>
@@ -1806,17 +1955,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32" s="7" t="n">
         <v>0</v>
@@ -1837,22 +1986,22 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="C33" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" s="7" t="n">
         <v>0</v>
@@ -1865,7 +2014,7 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>決定6</t>
+          <t>決定1・決定2</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr"/>
@@ -1878,14 +2027,14 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>0</v>
@@ -1901,7 +2050,7 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>決定1・決定2</t>
+          <t>決定3</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr"/>
@@ -1914,14 +2063,14 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>0</v>
@@ -1930,14 +2079,14 @@
         <v>0</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>決定3</t>
+          <t>決定3・決定8</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr"/>
@@ -1950,14 +2099,14 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>0</v>
@@ -1966,14 +2115,14 @@
         <v>0</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H36" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>決定3・決定8</t>
+          <t>決定3</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr"/>
@@ -1986,14 +2135,14 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>0</v>
@@ -2005,11 +2154,11 @@
         <v>0</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>決定3</t>
+          <t>決定8</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr"/>
@@ -2017,25 +2166,25 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>資料編</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>資料6 基本指針の新別表「確認すべき指標・状況」への対応</t>
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>0</v>
@@ -2045,7 +2194,7 @@
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>決定8</t>
+          <t>決定10</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr"/>
@@ -2058,65 +2207,65 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>資料6 基本指針の新別表「確認すべき指標・状況」への対応</t>
+          <t>資料7 図表番号一覧</t>
         </is>
       </c>
       <c r="C39" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>決定10</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr"/>
+      <c r="C40" s="15" t="n">
+        <v>88</v>
+      </c>
+      <c r="D40" s="15" t="n">
+        <v>58</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="F40" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="G40" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="D39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>決定10</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="inlineStr"/>
-      <c r="C40" s="13" t="n">
-        <v>90</v>
-      </c>
-      <c r="D40" s="13" t="n">
-        <v>63</v>
-      </c>
-      <c r="E40" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="F40" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="G40" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="H40" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
+      <c r="I40" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="J40" s="12" t="inlineStr"/>
+      <c r="J40" s="14" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
@@ -2127,10 +2276,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A2:L2"/>
     <mergeCell ref="A42:J42"/>
     <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A17:J17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2217,7 +2366,7 @@
           <t>決定7　調査の集計方法（未回答時の扱い）</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
@@ -2249,7 +2398,7 @@
           <t>決定2　認定率のシナリオ</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
@@ -2281,7 +2430,7 @@
           <t>決定1　人口推計の基礎と補正</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
@@ -2313,7 +2462,7 @@
           <t>決定5　第9期評価の範囲と暫定評価</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -2345,7 +2494,7 @@
           <t>決定6　調査に所見があるが対応する施策を確認できない5領域の扱い</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -2377,7 +2526,7 @@
           <t>決定4　代表KPIの目標値</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -2409,7 +2558,7 @@
           <t>決定12　概要版の仕様</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -2441,7 +2590,7 @@
           <t>決定3　サービス見込量と施設整備</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -2473,7 +2622,7 @@
           <t>決定8　保険料の設計</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -2505,7 +2654,7 @@
           <t>決定11　図表・自給率の掲載</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -2537,7 +2686,7 @@
           <t>決定9　圏域と訪問・通所困難地域</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -2569,7 +2718,7 @@
           <t>決定10　資料編の記載範囲</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -2635,14 +2784,14 @@
           <t>決定7・決定5・決定6・決定11</t>
         </is>
       </c>
-      <c r="C22" s="14" t="n"/>
-      <c r="D22" s="15" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="17" t="n"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
           <t>調査確定値の反映、第3章の評価、第5章の施策体系の確定</t>
         </is>
       </c>
-      <c r="F22" s="15" t="n"/>
+      <c r="F22" s="17" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -2655,14 +2804,14 @@
           <t>決定1・決定2・決定4・決定12・決定9</t>
         </is>
       </c>
-      <c r="C23" s="14" t="n"/>
-      <c r="D23" s="15" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="17" t="n"/>
       <c r="E23" s="5" t="inlineStr">
         <is>
           <t>第6章第1節の確定、第2段階の再計算、概要版の設計</t>
         </is>
       </c>
-      <c r="F23" s="15" t="n"/>
+      <c r="F23" s="17" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
@@ -2675,14 +2824,14 @@
           <t>決定3・決定8・決定10</t>
         </is>
       </c>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="15" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="17" t="n"/>
       <c r="E24" s="5" t="inlineStr">
         <is>
           <t>第6章第2〜7節の確定、資料編の確定</t>
         </is>
       </c>
-      <c r="F24" s="15" t="n"/>
+      <c r="F24" s="17" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -2695,14 +2844,14 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="15" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="17" t="n"/>
       <c r="E25" s="5" t="inlineStr">
         <is>
           <t>計画素案の確定、概要版（パブリックコメント用）の作成</t>
         </is>
       </c>
-      <c r="F25" s="15" t="n"/>
+      <c r="F25" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">

--- a/output/第10期計画_発注者確認事項一覧.xlsx
+++ b/output/第10期計画_発注者確認事項一覧.xlsx
@@ -594,7 +594,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議58件／要確認16件／未対応7件／要内訳1件／暫定6件 の計88箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
+          <t>計画素案に残る要協議96件／要確認18件／未対応7件／要内訳1件／暫定6件 の計128箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議58件／要確認16件／未対応7件／要内訳1件／暫定6件 の計88箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
+          <t>計画素案に残る要協議96件／要確認18件／未対応7件／要内訳1件／暫定6件 の計128箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
         </is>
       </c>
     </row>
@@ -1492,14 +1492,14 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>注1）箇所数の合計は87箇所である。本文の88箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る1箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
+          <t>注1）箇所数の合計は87箇所である。本文の128箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る41箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>【章節別の未決箇所（88箇所の所在）】</t>
+          <t>【章節別の未決箇所（128箇所の所在）】</t>
         </is>
       </c>
     </row>
@@ -2103,13 +2103,13 @@
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F36" s="7" t="n">
         <v>0</v>
@@ -2243,13 +2243,13 @@
       </c>
       <c r="B40" s="14" t="inlineStr"/>
       <c r="C40" s="15" t="n">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="D40" s="15" t="n">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F40" s="15" t="n">
         <v>7</v>

--- a/output/第10期計画_発注者確認事項一覧.xlsx
+++ b/output/第10期計画_発注者確認事項一覧.xlsx
@@ -594,7 +594,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議96件／要確認18件／未対応7件／要内訳1件／暫定6件 の計128箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
+          <t>計画素案に残る要協議105件／要確認19件／未対応7件／要内訳1件／暫定6件 の計138箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議96件／要確認18件／未対応7件／要内訳1件／暫定6件 の計128箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
+          <t>計画素案に残る要協議105件／要確認19件／未対応7件／要内訳1件／暫定6件 の計138箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
         </is>
       </c>
     </row>
@@ -1492,14 +1492,14 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>注1）箇所数の合計は87箇所である。本文の128箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る41箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
+          <t>注1）箇所数の合計は87箇所である。本文の138箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る51箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>【章節別の未決箇所（128箇所の所在）】</t>
+          <t>【章節別の未決箇所（138箇所の所在）】</t>
         </is>
       </c>
     </row>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" s="7" t="n">
         <v>0</v>
@@ -2243,13 +2243,13 @@
       </c>
       <c r="B40" s="14" t="inlineStr"/>
       <c r="C40" s="15" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D40" s="15" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F40" s="15" t="n">
         <v>7</v>

--- a/output/第10期計画_発注者確認事項一覧.xlsx
+++ b/output/第10期計画_発注者確認事項一覧.xlsx
@@ -594,7 +594,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議105件／要確認19件／未対応7件／要内訳1件／暫定6件 の計138箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
+          <t>計画素案に残る要協議106件／要確認20件／未対応7件／要内訳1件／暫定6件 の計140箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議105件／要確認19件／未対応7件／要内訳1件／暫定6件 の計138箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
+          <t>計画素案に残る要協議106件／要確認20件／未対応7件／要内訳1件／暫定6件 の計140箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
         </is>
       </c>
     </row>
@@ -1492,14 +1492,14 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>注1）箇所数の合計は87箇所である。本文の138箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る51箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
+          <t>注1）箇所数の合計は87箇所である。本文の140箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る53箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>【章節別の未決箇所（138箇所の所在）】</t>
+          <t>【章節別の未決箇所（140箇所の所在）】</t>
         </is>
       </c>
     </row>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>0</v>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="7" t="n">
         <v>0</v>
@@ -2243,13 +2243,13 @@
       </c>
       <c r="B40" s="14" t="inlineStr"/>
       <c r="C40" s="15" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D40" s="15" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F40" s="15" t="n">
         <v>7</v>
